--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>42.95</v>
+        <v>41.97</v>
       </c>
       <c r="F2" t="n">
-        <v>40.37</v>
+        <v>38.56</v>
       </c>
       <c r="G2" t="n">
-        <v>1.064</v>
+        <v>1.089</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3994,13 +3994,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>56.31</v>
+        <v>54.12</v>
       </c>
       <c r="F3" t="n">
-        <v>57.26</v>
+        <v>54.53</v>
       </c>
       <c r="G3" t="n">
-        <v>0.983</v>
+        <v>0.992</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4029,17 +4029,17 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>41.4</v>
+        <v>21.52</v>
       </c>
       <c r="F4" t="n">
-        <v>42.45</v>
+        <v>40.26</v>
       </c>
       <c r="G4" t="n">
-        <v>0.975</v>
+        <v>0.535</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>DISTRIBUTION</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -4064,13 +4064,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>45.33</v>
+        <v>50.36</v>
       </c>
       <c r="F5" t="n">
-        <v>50.06</v>
+        <v>51.34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.906</v>
+        <v>0.981</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2" t="n">
         <v>22</v>
-      </c>
-      <c r="D2" t="n">
-        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,17 +4152,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4170,20 +4170,20 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
@@ -4204,13 +4204,13 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>16</v>
       </c>
-      <c r="C5" t="n">
-        <v>27</v>
-      </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4224,17 +4224,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4248,17 +4248,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4272,17 +4272,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4344,17 +4344,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4368,17 +4368,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4392,21 +4392,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4416,17 +4416,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4440,14 +4440,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -4464,17 +4464,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4482,23 +4482,23 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4512,14 +4512,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>-3</v>
@@ -4536,17 +4536,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4584,17 +4584,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4602,23 +4602,23 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4632,17 +4632,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4656,14 +4656,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
         <v>-10</v>
@@ -4674,23 +4674,23 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C26" t="n">
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>-18</v>
+        <v>-15</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4728,17 +4728,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>-23</v>
+        <v>-18</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4746,23 +4746,23 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>-24</v>
+        <v>-22</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Comparing 2026-08-28 vs 2026-08-21 (≥5 trading days back)</t>
+          <t>Comparing 2026-09-04 vs 2026-08-28 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>41.97</v>
+        <v>37.36</v>
       </c>
       <c r="F2" t="n">
-        <v>38.56</v>
+        <v>41.34</v>
       </c>
       <c r="G2" t="n">
-        <v>1.089</v>
+        <v>0.904</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3994,13 +3994,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>54.12</v>
+        <v>61.76</v>
       </c>
       <c r="F3" t="n">
-        <v>54.53</v>
+        <v>54.96</v>
       </c>
       <c r="G3" t="n">
-        <v>0.992</v>
+        <v>1.124</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4029,17 +4029,17 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>21.52</v>
+        <v>44.4</v>
       </c>
       <c r="F4" t="n">
-        <v>40.26</v>
+        <v>40.89</v>
       </c>
       <c r="G4" t="n">
-        <v>0.535</v>
+        <v>1.086</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DISTRIBUTION</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -4064,13 +4064,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>50.36</v>
+        <v>52.41</v>
       </c>
       <c r="F5" t="n">
-        <v>51.34</v>
+        <v>50.67</v>
       </c>
       <c r="G5" t="n">
-        <v>0.981</v>
+        <v>1.034</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,17 +4152,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4176,17 +4176,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4200,17 +4200,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4224,17 +4224,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4248,17 +4248,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4266,20 +4266,20 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4320,21 +4320,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4344,21 +4344,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4368,21 +4368,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4392,17 +4392,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4416,14 +4416,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -4440,14 +4440,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -4464,14 +4464,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4482,20 +4482,20 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -4516,17 +4516,17 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" t="n">
         <v>6</v>
       </c>
-      <c r="C18" t="n">
-        <v>3</v>
-      </c>
       <c r="D18" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4536,21 +4536,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4560,21 +4560,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4584,38 +4584,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" t="n">
         <v>-4</v>
@@ -4632,17 +4632,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4656,17 +4656,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4674,23 +4674,23 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4728,17 +4728,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>-18</v>
+        <v>-10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4746,23 +4746,23 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>-22</v>
+        <v>-11</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Comparing 2026-09-04 vs 2026-08-28 (≥5 trading days back)</t>
+          <t>Comparing 2026-09-11 vs 2026-09-04 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>37.36</v>
+        <v>48.8</v>
       </c>
       <c r="F2" t="n">
-        <v>41.34</v>
+        <v>43.59</v>
       </c>
       <c r="G2" t="n">
-        <v>0.904</v>
+        <v>1.119</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3994,17 +3994,17 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>61.76</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>54.96</v>
+        <v>55.17</v>
       </c>
       <c r="G3" t="n">
-        <v>1.124</v>
+        <v>1.281</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>ACCUM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -4029,17 +4029,17 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>44.4</v>
+        <v>32.13</v>
       </c>
       <c r="F4" t="n">
-        <v>40.89</v>
+        <v>38.48</v>
       </c>
       <c r="G4" t="n">
-        <v>1.086</v>
+        <v>0.835</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>WEAK</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -4064,13 +4064,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>52.41</v>
+        <v>43.44</v>
       </c>
       <c r="F5" t="n">
-        <v>50.67</v>
+        <v>49.21</v>
       </c>
       <c r="G5" t="n">
-        <v>1.034</v>
+        <v>0.883</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4146,23 +4146,23 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4176,17 +4176,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4200,17 +4200,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4224,17 +4224,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4242,23 +4242,23 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4266,23 +4266,23 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4320,21 +4320,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4344,21 +4344,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4368,21 +4368,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4392,17 +4392,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4416,14 +4416,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -4440,14 +4440,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -4464,17 +4464,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4488,17 +4488,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4512,17 +4512,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4540,17 +4540,17 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
         <v>9</v>
       </c>
-      <c r="C19" t="n">
-        <v>7</v>
-      </c>
       <c r="D19" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4560,21 +4560,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4584,41 +4584,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4632,17 +4632,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D23" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4656,17 +4656,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>-9</v>
+        <v>-16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10</v>
+        <v>-22</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4728,17 +4728,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>-10</v>
+        <v>-24</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4746,37 +4746,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>FINANCE</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>23</v>
-      </c>
-      <c r="C28" t="n">
-        <v>12</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-11</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ROTATING_OUT</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Comparing 2026-09-11 vs 2026-09-04 (≥5 trading days back)</t>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Comparing 2026-09-18 vs 2026-09-11 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>48.8</v>
+        <v>40.54</v>
       </c>
       <c r="F2" t="n">
-        <v>43.59</v>
+        <v>45.16</v>
       </c>
       <c r="G2" t="n">
-        <v>1.119</v>
+        <v>0.898</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3994,17 +3994,17 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>70.68000000000001</v>
+        <v>26.33</v>
       </c>
       <c r="F3" t="n">
-        <v>55.17</v>
+        <v>57.28</v>
       </c>
       <c r="G3" t="n">
-        <v>1.281</v>
+        <v>0.46</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>DISTRIBUTION</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -4029,17 +4029,17 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>32.13</v>
+        <v>42.62</v>
       </c>
       <c r="F4" t="n">
-        <v>38.48</v>
+        <v>37.46</v>
       </c>
       <c r="G4" t="n">
-        <v>0.835</v>
+        <v>1.138</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>WEAK</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -4064,13 +4064,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>43.44</v>
+        <v>49.19</v>
       </c>
       <c r="F5" t="n">
-        <v>49.21</v>
+        <v>46.72</v>
       </c>
       <c r="G5" t="n">
-        <v>0.883</v>
+        <v>1.053</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4146,23 +4146,23 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4176,14 +4176,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -4200,14 +4200,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
@@ -4224,17 +4224,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4242,23 +4242,23 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4266,23 +4266,23 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,14 +4296,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
@@ -4320,21 +4320,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4344,21 +4344,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4368,21 +4368,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4396,13 +4396,13 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4416,17 +4416,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4440,21 +4440,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4464,21 +4464,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4488,21 +4488,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4512,21 +4512,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4536,17 +4536,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4578,23 +4578,23 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4608,17 +4608,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4626,23 +4626,23 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C23" t="n">
         <v>16</v>
       </c>
       <c r="D23" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4656,17 +4656,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4728,17 +4728,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Comparing 2026-09-18 vs 2026-09-11 (≥5 trading days back)</t>
+          <t>Comparing 2026-09-25 vs 2026-09-18 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>40.54</v>
+        <v>42.64</v>
       </c>
       <c r="F2" t="n">
-        <v>45.16</v>
+        <v>44.78</v>
       </c>
       <c r="G2" t="n">
-        <v>0.898</v>
+        <v>0.952</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3994,17 +3994,17 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>26.33</v>
+        <v>69.52</v>
       </c>
       <c r="F3" t="n">
-        <v>57.28</v>
+        <v>58.66</v>
       </c>
       <c r="G3" t="n">
-        <v>0.46</v>
+        <v>1.185</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DISTRIBUTION</t>
+          <t>ACCUM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -4029,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>42.62</v>
+        <v>39.88</v>
       </c>
       <c r="F4" t="n">
-        <v>37.46</v>
+        <v>36.85</v>
       </c>
       <c r="G4" t="n">
-        <v>1.138</v>
+        <v>1.082</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4064,13 +4064,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>49.19</v>
+        <v>42.91</v>
       </c>
       <c r="F5" t="n">
-        <v>46.72</v>
+        <v>45.29</v>
       </c>
       <c r="G5" t="n">
-        <v>1.053</v>
+        <v>0.948</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,17 +4152,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4176,41 +4176,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" t="n">
         <v>10</v>
       </c>
-      <c r="C4" t="n">
-        <v>24</v>
-      </c>
-      <c r="D4" t="n">
-        <v>14</v>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4224,17 +4224,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4242,23 +4242,23 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4266,23 +4266,23 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4324,17 +4324,17 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" t="n">
         <v>18</v>
       </c>
-      <c r="C10" t="n">
-        <v>20</v>
-      </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4344,21 +4344,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4368,21 +4368,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4392,21 +4392,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-2</v>
-      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4416,17 +4416,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4440,21 +4440,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4464,21 +4464,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4488,21 +4488,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4512,21 +4512,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4536,21 +4536,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4578,23 +4578,23 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4608,17 +4608,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4626,23 +4626,23 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4656,14 +4656,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
         <v>-12</v>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4722,23 +4722,23 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Comparing 2026-09-25 vs 2026-09-18 (≥5 trading days back)</t>
+          <t>Comparing 2026-10-01 vs 2026-09-25 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,17 +3959,17 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>42.64</v>
+        <v>54.1</v>
       </c>
       <c r="F2" t="n">
-        <v>44.78</v>
+        <v>46.84</v>
       </c>
       <c r="G2" t="n">
-        <v>0.952</v>
+        <v>1.155</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>ACCUM</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3994,17 +3994,17 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>69.52</v>
+        <v>46.47</v>
       </c>
       <c r="F3" t="n">
-        <v>58.66</v>
+        <v>59.15</v>
       </c>
       <c r="G3" t="n">
-        <v>1.185</v>
+        <v>0.786</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>WEAK</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -4029,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>39.88</v>
+        <v>38.78</v>
       </c>
       <c r="F4" t="n">
-        <v>36.85</v>
+        <v>37.92</v>
       </c>
       <c r="G4" t="n">
-        <v>1.082</v>
+        <v>1.023</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4064,13 +4064,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>42.91</v>
+        <v>38.7</v>
       </c>
       <c r="F5" t="n">
-        <v>45.29</v>
+        <v>42.87</v>
       </c>
       <c r="G5" t="n">
-        <v>0.948</v>
+        <v>0.903</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,17 +4152,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4176,17 +4176,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4194,23 +4194,23 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4224,17 +4224,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4248,25 +4248,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" t="n">
         <v>7</v>
       </c>
-      <c r="C7" t="n">
-        <v>12</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4276,13 +4276,13 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
         <v>12</v>
       </c>
-      <c r="C8" t="n">
-        <v>16</v>
-      </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4314,20 +4314,20 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -4344,14 +4344,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -4362,27 +4362,27 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4392,21 +4392,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4416,17 +4416,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4440,17 +4440,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4458,23 +4458,23 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4488,17 +4488,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4516,13 +4516,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D20" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4588,10 +4588,10 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
         <v>11</v>
-      </c>
-      <c r="C21" t="n">
-        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>-5</v>
@@ -4608,14 +4608,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
         <v>-6</v>
@@ -4632,17 +4632,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4656,17 +4656,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C26" t="n">
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4722,23 +4722,23 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Comparing 2026-10-01 vs 2026-09-25 (≥5 trading days back)</t>
+          <t>Comparing 2026-10-09 vs 2026-10-01 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>54.1</v>
+        <v>58.76</v>
       </c>
       <c r="F2" t="n">
-        <v>46.84</v>
+        <v>49.26</v>
       </c>
       <c r="G2" t="n">
-        <v>1.155</v>
+        <v>1.193</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3994,17 +3994,17 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>46.47</v>
+        <v>62.95</v>
       </c>
       <c r="F3" t="n">
-        <v>59.15</v>
+        <v>59.27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.786</v>
+        <v>1.062</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WEAK</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -4029,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>38.78</v>
+        <v>41.06</v>
       </c>
       <c r="F4" t="n">
-        <v>37.92</v>
+        <v>38.58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.023</v>
+        <v>1.064</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4064,17 +4064,17 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>38.7</v>
+        <v>33</v>
       </c>
       <c r="F5" t="n">
-        <v>42.87</v>
+        <v>41.38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.903</v>
+        <v>0.798</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>WEAK</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -4090,7 +4090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,17 +4152,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4176,17 +4176,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="n">
         <v>14</v>
-      </c>
-      <c r="C4" t="n">
-        <v>25</v>
-      </c>
-      <c r="D4" t="n">
-        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4200,17 +4200,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4218,23 +4218,23 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4248,17 +4248,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" t="n">
         <v>9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>16</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4272,17 +4272,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4344,17 +4344,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4362,44 +4362,44 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -4416,14 +4416,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -4440,14 +4440,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -4458,23 +4458,23 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -4512,14 +4512,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>-2</v>
@@ -4536,17 +4536,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4584,17 +4584,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4608,17 +4608,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4632,17 +4632,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4656,17 +4656,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4722,23 +4722,23 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4749,10 +4749,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Comparing 2026-10-09 vs 2026-10-01 (≥5 trading days back)</t>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Comparing 2026-10-16 vs 2026-10-09 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,17 +3959,17 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>58.76</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>49.26</v>
+        <v>49.85</v>
       </c>
       <c r="G2" t="n">
-        <v>1.193</v>
+        <v>1.043</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3994,13 +3994,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>62.95</v>
+        <v>58.7</v>
       </c>
       <c r="F3" t="n">
-        <v>59.27</v>
+        <v>58.03</v>
       </c>
       <c r="G3" t="n">
-        <v>1.062</v>
+        <v>1.012</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4029,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>41.06</v>
+        <v>32.67</v>
       </c>
       <c r="F4" t="n">
-        <v>38.58</v>
+        <v>38.13</v>
       </c>
       <c r="G4" t="n">
-        <v>1.064</v>
+        <v>0.857</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4064,17 +4064,17 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>51.88</v>
       </c>
       <c r="F5" t="n">
-        <v>41.38</v>
+        <v>42.58</v>
       </c>
       <c r="G5" t="n">
-        <v>0.798</v>
+        <v>1.218</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WEAK</t>
+          <t>ACCUM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -4090,7 +4090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4146,23 +4146,23 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4176,17 +4176,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4200,14 +4200,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
@@ -4218,23 +4218,23 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4248,17 +4248,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4272,17 +4272,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4320,21 +4320,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4344,21 +4344,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4368,41 +4368,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4416,14 +4416,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -4440,14 +4440,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -4464,17 +4464,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4488,21 +4488,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4512,41 +4512,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4584,17 +4584,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4602,23 +4602,23 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C22" t="n">
         <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4632,14 +4632,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D23" t="n">
         <v>-9</v>
@@ -4660,13 +4660,13 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="n">
         <v>12</v>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
       <c r="D24" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4722,23 +4722,23 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>-22</v>
+        <v>-18</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4749,38 +4749,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>RETAIL</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>25</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Comparing 2026-10-16 vs 2026-10-09 (≥5 trading days back)</t>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Comparing 2026-10-23 vs 2026-10-16 (≥5 trading days back)</t>
         </is>
       </c>
     </row>
